--- a/catalogo-produtos/importador/prateleira.xlsx
+++ b/catalogo-produtos/importador/prateleira.xlsx
@@ -61,7 +61,7 @@
     <t>só lojas</t>
   </si>
   <si>
-    <t>—</t>
+    <t>não</t>
   </si>
   <si>
     <t>892265418</t>

--- a/catalogo-produtos/importador/prateleira.xlsx
+++ b/catalogo-produtos/importador/prateleira.xlsx
@@ -61,7 +61,7 @@
     <t>só lojas</t>
   </si>
   <si>
-    <t>não</t>
+    <t>—</t>
   </si>
   <si>
     <t>892265418</t>
